--- a/Control_LAB/Lab_3/Lab_3.xlsx
+++ b/Control_LAB/Lab_3/Lab_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Semestre\Cursando\Control_LAB\Lab_3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFC0825-276D-42C9-8EB1-D84A4F7A81F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E1FDC6-E8FB-4039-8B79-867FFB36169B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>Ubicacion</t>
   </si>
@@ -102,16 +102,16 @@
     <t>CH2</t>
   </si>
   <si>
-    <t>PB4</t>
-  </si>
-  <si>
-    <t>PB5</t>
-  </si>
-  <si>
-    <t>CN7 - 19</t>
-  </si>
-  <si>
-    <t>CN7 - 13</t>
+    <t>PB6</t>
+  </si>
+  <si>
+    <t>PB7</t>
+  </si>
+  <si>
+    <t>CN10 - 13</t>
+  </si>
+  <si>
+    <t>CN11 - 21</t>
   </si>
 </sst>
 </file>
@@ -662,40 +662,48 @@
     </row>
     <row r="14" spans="8:15" x14ac:dyDescent="0.25">
       <c r="H14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="J14" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="K14" s="6" t="s">
         <v>0</v>
       </c>
       <c r="L14" s="4"/>
     </row>
     <row r="15" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="6">
+        <v>9</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="J15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="K15" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="16" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="6">
+        <v>9</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="J16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="K16" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H17" s="4"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
